--- a/game_stats.xlsx
+++ b/game_stats.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>grunt</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>步兵</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -546,177 +546,326 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>头顶红色小角</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>bomber</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>突击兵</t>
+          <t>bomber</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>尖头+粉色拖尾</t>
-        </is>
-      </c>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>flyer</t>
+          <t>fatso</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>飞行兵</t>
+          <t>fatso</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>紫色翅膀+推进器</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>swarm</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>重装兵</t>
+          <t>swarm</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>20</v>
-      </c>
       <c r="G5" s="3" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>蓝色护盾+肩甲</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>medic</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>medic</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>shielder</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>shielder</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>assassin</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>assassin</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>tankElite</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>tankElite</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>rangedElite</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>rangedElite</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>boss</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>500+Lv*50</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>双角+发光眼+光环</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>黄色底 = 可编辑，import 时会同步回代码</t>
         </is>
@@ -795,7 +944,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
